--- a/LISTAS/ma/BISAGRA MUNICION DISMAY.xlsx
+++ b/LISTAS/ma/BISAGRA MUNICION DISMAY.xlsx
@@ -731,14 +731,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="18" t="n">
-        <v>45180.4773211443</v>
+        <v>45253</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="17">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -780,26 +776,6 @@
       <c r="A11" s="16" t="n"/>
       <c r="E11" s="7" t="n"/>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
     <row r="32" ht="18" customHeight="1" s="17">
       <c r="A32" s="9" t="inlineStr">
         <is>
@@ -831,7 +807,7 @@
       </c>
       <c r="C33" s="15" t="n"/>
       <c r="D33" s="11" t="n">
-        <v>616.2430000000001</v>
+        <v>671.705</v>
       </c>
       <c r="E33" s="12" t="n"/>
       <c r="F33" s="12" t="n"/>
@@ -850,7 +826,7 @@
       </c>
       <c r="C34" s="15" t="n"/>
       <c r="D34" s="13" t="n">
-        <v>640.9930000000001</v>
+        <v>737.1420000000001</v>
       </c>
       <c r="E34" s="12" t="n"/>
       <c r="F34" s="12" t="n"/>
@@ -869,7 +845,7 @@
       </c>
       <c r="C35" s="15" t="n"/>
       <c r="D35" s="13" t="n">
-        <v>477.287</v>
+        <v>548.88</v>
       </c>
       <c r="E35" s="12" t="n"/>
       <c r="F35" s="12" t="n"/>
@@ -880,14 +856,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
     <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B35:C35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/BISAGRA MUNICION DISMAY.xlsx
+++ b/LISTAS/ma/BISAGRA MUNICION DISMAY.xlsx
@@ -731,7 +731,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="18" t="n">
-        <v>45253</v>
+        <v>45256</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>

--- a/LISTAS/ma/BISAGRA MUNICION DISMAY.xlsx
+++ b/LISTAS/ma/BISAGRA MUNICION DISMAY.xlsx
@@ -731,7 +731,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="18" t="n">
-        <v>45256</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>

--- a/LISTAS/ma/BISAGRA MUNICION DISMAY.xlsx
+++ b/LISTAS/ma/BISAGRA MUNICION DISMAY.xlsx
@@ -731,10 +731,14 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="18" t="n">
-        <v>45266</v>
+        <v>45261.57768865743</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="17">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -776,6 +780,26 @@
       <c r="A11" s="16" t="n"/>
       <c r="E11" s="7" t="n"/>
     </row>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
     <row r="32" ht="18" customHeight="1" s="17">
       <c r="A32" s="9" t="inlineStr">
         <is>
@@ -807,7 +831,7 @@
       </c>
       <c r="C33" s="15" t="n"/>
       <c r="D33" s="11" t="n">
-        <v>671.705</v>
+        <v>750</v>
       </c>
       <c r="E33" s="12" t="n"/>
       <c r="F33" s="12" t="n"/>
@@ -826,7 +850,7 @@
       </c>
       <c r="C34" s="15" t="n"/>
       <c r="D34" s="13" t="n">
-        <v>737.1420000000001</v>
+        <v>891.9400000000001</v>
       </c>
       <c r="E34" s="12" t="n"/>
       <c r="F34" s="12" t="n"/>
@@ -845,7 +869,7 @@
       </c>
       <c r="C35" s="15" t="n"/>
       <c r="D35" s="13" t="n">
-        <v>548.88</v>
+        <v>664.14</v>
       </c>
       <c r="E35" s="12" t="n"/>
       <c r="F35" s="12" t="n"/>
@@ -856,14 +880,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B32:C32"/>
     <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A10:D10"/>
     <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B35:C35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/BISAGRA MUNICION DISMAY.xlsx
+++ b/LISTAS/ma/BISAGRA MUNICION DISMAY.xlsx
@@ -731,14 +731,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="18" t="n">
-        <v>45261.57768865743</v>
+        <v>45286</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="17">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -780,26 +776,6 @@
       <c r="A11" s="16" t="n"/>
       <c r="E11" s="7" t="n"/>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
     <row r="32" ht="18" customHeight="1" s="17">
       <c r="A32" s="9" t="inlineStr">
         <is>
@@ -831,7 +807,7 @@
       </c>
       <c r="C33" s="15" t="n"/>
       <c r="D33" s="11" t="n">
-        <v>750</v>
+        <v>671.705</v>
       </c>
       <c r="E33" s="12" t="n"/>
       <c r="F33" s="12" t="n"/>
@@ -850,7 +826,7 @@
       </c>
       <c r="C34" s="15" t="n"/>
       <c r="D34" s="13" t="n">
-        <v>891.9400000000001</v>
+        <v>737.1420000000001</v>
       </c>
       <c r="E34" s="12" t="n"/>
       <c r="F34" s="12" t="n"/>
@@ -869,7 +845,7 @@
       </c>
       <c r="C35" s="15" t="n"/>
       <c r="D35" s="13" t="n">
-        <v>664.14</v>
+        <v>548.88</v>
       </c>
       <c r="E35" s="12" t="n"/>
       <c r="F35" s="12" t="n"/>
@@ -880,14 +856,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="B33:C33"/>
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B34:C34"/>
     <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="B34:C34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="5" horizontalDpi="0" verticalDpi="0"/>
